--- a/data/trans_camb/IP24_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 2,53</t>
+          <t>-17,36; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 9,83</t>
+          <t>-14,82; 8,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 30,52</t>
+          <t>-8,82; 31,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 1,53</t>
+          <t>-16,8; 0,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 0,44</t>
+          <t>-17,69; -0,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 14,52</t>
+          <t>-8,55; 14,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -0,68</t>
+          <t>-13,67; -0,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 0,92</t>
+          <t>-13,06; 1,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 17,87</t>
+          <t>-4,44; 18,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 16,15</t>
+          <t>-57,77; 16,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 52,82</t>
+          <t>-49,74; 41,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 155,55</t>
+          <t>-35,35; 154,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 12,88</t>
+          <t>-67,53; 5,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,97; 5,2</t>
+          <t>-72,03; 4,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 96,34</t>
+          <t>-38,54; 91,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,35; -2,85</t>
+          <t>-54,21; -3,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 5,25</t>
+          <t>-52,14; 7,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 94,11</t>
+          <t>-17,88; 99,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,45</t>
+          <t>-8,94; 0,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 0,31</t>
+          <t>-8,86; 0,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 11,91</t>
+          <t>-7,99; 13,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -2,45</t>
+          <t>-10,68; -2,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -3,43</t>
+          <t>-11,81; -4,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 2,31</t>
+          <t>-9,26; 1,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -2,34</t>
+          <t>-8,66; -2,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; -3,23</t>
+          <t>-9,14; -3,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 4,93</t>
+          <t>-7,16; 5,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 2,29</t>
+          <t>-31,01; 2,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 1,48</t>
+          <t>-31,43; 1,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 49,03</t>
+          <t>-29,74; 50,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,59; -12,42</t>
+          <t>-43,46; -10,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -17,13</t>
+          <t>-48,25; -20,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 12,72</t>
+          <t>-37,78; 7,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,7; -10,19</t>
+          <t>-33,04; -9,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,4; -14,13</t>
+          <t>-35,39; -13,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 22,0</t>
+          <t>-28,65; 21,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 2,35</t>
+          <t>-13,0; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 6,2</t>
+          <t>-8,21; 6,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 0,63</t>
+          <t>-14,45; 0,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,83; -3,4</t>
+          <t>-18,04; -2,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 4,48</t>
+          <t>-11,01; 4,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,62; -4,09</t>
+          <t>-18,58; -3,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -2,37</t>
+          <t>-13,06; -3,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 3,42</t>
+          <t>-7,15; 3,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -3,25</t>
+          <t>-14,27; -3,72</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 12,1</t>
+          <t>-48,36; 6,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 31,97</t>
+          <t>-30,08; 30,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 4,02</t>
+          <t>-51,68; 1,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,65; -14,55</t>
+          <t>-57,95; -11,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 19,11</t>
+          <t>-33,52; 20,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -15,45</t>
+          <t>-60,3; -14,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,14; -10,36</t>
+          <t>-46,23; -12,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 15,78</t>
+          <t>-25,25; 13,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,78; -13,54</t>
+          <t>-50,38; -15,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -1,05</t>
+          <t>-9,12; -1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,31</t>
+          <t>-6,98; 0,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 10,03</t>
+          <t>-7,33; 9,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -3,95</t>
+          <t>-10,85; -4,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -3,31</t>
+          <t>-9,97; -3,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -0,35</t>
+          <t>-9,05; -0,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -3,72</t>
+          <t>-8,77; -3,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -2,57</t>
+          <t>-7,28; -2,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,3</t>
+          <t>-7,15; 1,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -4,38</t>
+          <t>-33,24; -6,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 1,27</t>
+          <t>-25,87; 0,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 41,98</t>
+          <t>-27,94; 40,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,71; -18,27</t>
+          <t>-42,81; -18,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,93; -15,47</t>
+          <t>-39,61; -14,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -1,16</t>
+          <t>-36,6; -1,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,79; -16,07</t>
+          <t>-34,25; -16,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,74; -11,07</t>
+          <t>-28,65; -11,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 5,73</t>
+          <t>-28,39; 5,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 2,43</t>
+          <t>-17,47; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 8,82</t>
+          <t>-13,83; 9,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 31,3</t>
+          <t>-8,29; 30,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 0,44</t>
+          <t>-16,85; 1,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -0,07</t>
+          <t>-18,72; 0,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 14,67</t>
+          <t>-8,48; 15,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -0,61</t>
+          <t>-14,47; -0,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 1,58</t>
+          <t>-13,67; 1,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 18,05</t>
+          <t>-5,72; 19,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 16,06</t>
+          <t>-56,16; 13,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 41,49</t>
+          <t>-48,75; 49,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 154,03</t>
+          <t>-33,79; 155,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 5,32</t>
+          <t>-68,61; 13,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 4,4</t>
+          <t>-75,16; 4,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 91,04</t>
+          <t>-35,09; 107,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,21; -3,09</t>
+          <t>-56,38; -4,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 7,88</t>
+          <t>-52,66; 9,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 99,92</t>
+          <t>-25,31; 95,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,44</t>
+          <t>-9,48; 0,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,45</t>
+          <t>-9,49; 0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 13,25</t>
+          <t>-8,21; 12,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -2,3</t>
+          <t>-10,31; -2,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -4,17</t>
+          <t>-11,93; -3,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,44</t>
+          <t>-9,31; 1,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -2,19</t>
+          <t>-8,25; -2,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -3,01</t>
+          <t>-8,9; -2,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 5,13</t>
+          <t>-7,27; 3,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 2,51</t>
+          <t>-32,64; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 1,88</t>
+          <t>-32,56; 1,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 50,76</t>
+          <t>-30,1; 48,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,46; -10,7</t>
+          <t>-42,02; -12,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -20,08</t>
+          <t>-47,95; -17,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 7,43</t>
+          <t>-39,12; 8,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,04; -9,92</t>
+          <t>-32,08; -10,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,39; -13,44</t>
+          <t>-34,6; -12,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 21,73</t>
+          <t>-29,26; 17,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 1,19</t>
+          <t>-13,11; 1,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 6,33</t>
+          <t>-8,74; 6,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 0,01</t>
+          <t>-14,36; 0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,04; -2,78</t>
+          <t>-17,88; -3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 4,48</t>
+          <t>-10,92; 3,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,58; -3,59</t>
+          <t>-18,87; -3,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -3,04</t>
+          <t>-13,47; -3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,23</t>
+          <t>-7,25; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -3,72</t>
+          <t>-14,3; -3,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 6,39</t>
+          <t>-46,68; 5,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 30,33</t>
+          <t>-31,91; 32,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 1,67</t>
+          <t>-51,82; 5,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,95; -11,48</t>
+          <t>-57,48; -13,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 20,9</t>
+          <t>-33,63; 15,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,3; -14,0</t>
+          <t>-59,73; -14,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,23; -12,61</t>
+          <t>-46,28; -12,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 13,91</t>
+          <t>-26,09; 14,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,38; -15,98</t>
+          <t>-49,82; -15,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -1,51</t>
+          <t>-9,05; -1,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 0,18</t>
+          <t>-7,13; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 9,49</t>
+          <t>-7,38; 8,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -4,02</t>
+          <t>-10,72; -3,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -3,32</t>
+          <t>-10,16; -3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,32</t>
+          <t>-9,49; -1,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -3,57</t>
+          <t>-8,64; -3,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,53</t>
+          <t>-7,37; -2,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1,28</t>
+          <t>-7,04; 1,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -6,87</t>
+          <t>-32,4; -7,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 0,61</t>
+          <t>-26,49; 1,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 40,22</t>
+          <t>-27,95; 36,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,81; -18,27</t>
+          <t>-43,12; -18,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,61; -14,75</t>
+          <t>-39,79; -14,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,6; -1,38</t>
+          <t>-37,34; -3,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -16,31</t>
+          <t>-33,94; -16,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; -11,17</t>
+          <t>-28,83; -10,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 5,98</t>
+          <t>-27,82; 6,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-7,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-7,25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,63</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,37</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>-2,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 2,61</t>
+          <t>-16,41; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 9,47</t>
+          <t>-18,5; 0,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 30,78</t>
+          <t>-10,24; 11,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 1,58</t>
+          <t>-17,35; 2,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 0,29</t>
+          <t>-13,27; 9,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 15,35</t>
+          <t>-16,85; 6,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -0,87</t>
+          <t>-13,9; -0,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 1,54</t>
+          <t>-13,69; 0,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 19,05</t>
+          <t>-10,4; 6,06</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-38,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-44,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-29,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-10,74%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-38,19%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-44,65%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>-20,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>-10,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 13,97</t>
+          <t>-66,17; 12,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 49,44</t>
+          <t>-73,97; 5,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 155,4</t>
+          <t>-41,28; 81,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 13,88</t>
+          <t>-56,24; 16,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 4,86</t>
+          <t>-47,19; 52,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 107,61</t>
+          <t>-57,14; 33,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,38; -4,54</t>
+          <t>-54,35; -2,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 9,47</t>
+          <t>-52,89; 5,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 95,77</t>
+          <t>-40,45; 32,19</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-6,35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-7,91</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-6,09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-4,28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,91</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-7,64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-6,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,11</t>
+          <t>-10,35; -2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 0,14</t>
+          <t>-11,6; -3,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 12,34</t>
+          <t>-10,56; -0,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -2,42</t>
+          <t>-8,87; 0,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -3,67</t>
+          <t>-8,43; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 1,67</t>
+          <t>-12,13; -2,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -2,31</t>
+          <t>-8,51; -2,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -2,92</t>
+          <t>-9,09; -3,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 3,78</t>
+          <t>-10,24; -3,28</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-28,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-35,06%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-26,98%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-16,43%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-16,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,59%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-28,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-35,06%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,75%</t>
+          <t>-29,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,99%</t>
+          <t>-28,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 0,91</t>
+          <t>-42,59; -12,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 1,05</t>
+          <t>-47,53; -17,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 48,62</t>
+          <t>-43,15; 1,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,02; -12,03</t>
+          <t>-31,61; 2,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -17,06</t>
+          <t>-30,13; 1,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 8,11</t>
+          <t>-43,36; -11,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,08; -10,08</t>
+          <t>-32,7; -10,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,6; -12,78</t>
+          <t>-35,4; -14,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 17,22</t>
+          <t>-39,45; -13,57</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-10,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-12,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-5,76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,33</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,63</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-10,51</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,23</t>
+          <t>-8,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,89</t>
+          <t>-9,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 1,09</t>
+          <t>-17,83; -3,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 6,33</t>
+          <t>-10,14; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 0,96</t>
+          <t>-19,26; -4,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -3,3</t>
+          <t>-12,76; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 3,56</t>
+          <t>-8,41; 6,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -3,75</t>
+          <t>-15,17; -1,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,47; -3,08</t>
+          <t>-13,01; -2,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 3,24</t>
+          <t>-7,5; 3,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -3,7</t>
+          <t>-14,69; -4,58</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-38,3%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-10,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-44,02%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-24,2%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-5,58%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-27,85%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-38,3%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-10,84%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-40,91%</t>
+          <t>-33,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,81%</t>
+          <t>-39,07%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 5,71</t>
+          <t>-56,65; -14,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 32,13</t>
+          <t>-32,06; 19,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 5,88</t>
+          <t>-62,29; -19,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -13,03</t>
+          <t>-48,41; 12,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 15,16</t>
+          <t>-31,01; 31,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,73; -14,38</t>
+          <t>-54,99; -4,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,28; -12,66</t>
+          <t>-46,14; -10,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 14,11</t>
+          <t>-26,87; 15,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,82; -15,38</t>
+          <t>-51,94; -18,3</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-7,38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,79</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-4,97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,34</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,84</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-7,38</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,53</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-7,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-7,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -1,79</t>
+          <t>-10,88; -3,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,41</t>
+          <t>-9,99; -3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 8,52</t>
+          <t>-10,19; -1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,72; -3,94</t>
+          <t>-8,28; -1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -3,15</t>
+          <t>-7,23; 0,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -1,03</t>
+          <t>-11,09; -3,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -3,66</t>
+          <t>-8,62; -3,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,33</t>
+          <t>-7,62; -2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,42</t>
+          <t>-9,67; -4,33</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-31,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-28,01%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-29,1%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-19,64%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-13,19%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-7,25%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-31,62%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-28,01%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,36%</t>
+          <t>-29,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,65%</t>
+          <t>-29,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -7,15</t>
+          <t>-42,71; -18,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 1,72</t>
+          <t>-39,93; -15,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 36,27</t>
+          <t>-41,02; -8,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -18,37</t>
+          <t>-30,25; -4,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,79; -14,97</t>
+          <t>-26,46; 1,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,34; -3,23</t>
+          <t>-40,76; -15,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,94; -16,24</t>
+          <t>-33,79; -16,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,83; -10,04</t>
+          <t>-29,74; -11,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 6,29</t>
+          <t>-37,99; -18,34</t>
         </is>
       </c>
     </row>
